--- a/data/trans_bre/P1801_2016_2023-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P1801_2016_2023-Edad-trans_bre.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>19,31</t>
+          <t>21,8</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>116,15%</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,06; 20,47</t>
+          <t>7,85; 21,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,14; 29,55</t>
+          <t>11,94; 31,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22,45; 88,09</t>
+          <t>26,77; 91,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27,96; 189,21</t>
+          <t>49,23; 217,9</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2,67</t>
+          <t>7,73</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>22,75%</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,68; 24,3</t>
+          <t>13,46; 24,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,16; 12,08</t>
+          <t>0,06; 14,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40,0; 86,99</t>
+          <t>40,23; 89,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-30,42; 37,92</t>
+          <t>0,17; 49,69</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4,27</t>
+          <t>6,69</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>16,25%</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,64; 15,38</t>
+          <t>4,45; 15,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 9,81</t>
+          <t>1,4; 12,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,31; 39,62</t>
+          <t>9,72; 39,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 24,52</t>
+          <t>3,0; 32,12</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-12,12</t>
+          <t>4,76</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-18,24%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 9,06</t>
+          <t>-1,64; 9,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-34,9; 3,06</t>
+          <t>-0,18; 9,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 20,09</t>
+          <t>-3,08; 22,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-41,61; 6,02</t>
+          <t>-0,34; 18,91</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5,98</t>
+          <t>7,59</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>13,37%</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,15; 15,0</t>
+          <t>1,3; 14,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,18; 10,92</t>
+          <t>2,87; 12,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,36; 27,67</t>
+          <t>2,07; 26,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,02; 20,03</t>
+          <t>4,63; 23,64</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>12,95</t>
+          <t>2,39</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -901,22 +901,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,27; 14,87</t>
+          <t>0,86; 14,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 28,12</t>
+          <t>-2,83; 7,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,79; 23,6</t>
+          <t>1,18; 22,04</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 45,71</t>
+          <t>-4,18; 12,74</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-2,7</t>
+          <t>-1,74</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-3,67%</t>
+          <t>-2,38%</t>
         </is>
       </c>
     </row>
@@ -961,22 +961,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,77; 3,65</t>
+          <t>-10,55; 3,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 2,47</t>
+          <t>-7,08; 3,4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,58; 5,05</t>
+          <t>-13,49; 5,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,21; 3,61</t>
+          <t>-9,31; 4,96</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4,26</t>
+          <t>7,99</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>16,67%</t>
         </is>
       </c>
     </row>
@@ -1021,22 +1021,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,18; 13,09</t>
+          <t>8,06; 13,22</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 11,92</t>
+          <t>5,59; 10,49</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17,08; 28,89</t>
+          <t>16,93; 29,31</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-9,59; 23,45</t>
+          <t>11,42; 22,67</t>
         </is>
       </c>
     </row>
